--- a/Teams.xlsx
+++ b/Teams.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Кекс\Downloads\Telegram Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kekc/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FCF493D-C368-4398-9A82-5929D7DC4AA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B0F8ED1-A280-314B-B701-CD79FE0991D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16980" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ОМО_4" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ОМО_4!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ОМО_4!$A$1:$L$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="216">
   <si>
     <t>#</t>
   </si>
@@ -438,6 +438,255 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Индивидуальное задание</t>
+  </si>
+  <si>
+    <t>Сравнение случайного и стратифицированного разбиения выборки</t>
+  </si>
+  <si>
+    <t>Влияние числа признаков на время обучения</t>
+  </si>
+  <si>
+    <t>Влияние StandardScaler на метод опорных векторов</t>
+  </si>
+  <si>
+    <t>Мягкое распределение объектов по кластерам в GaussianMixture</t>
+  </si>
+  <si>
+    <t>Поиск аномалий во временном ряду с помощью скользящего z-score</t>
+  </si>
+  <si>
+    <t>Оценка разброса качества по десяти случайным разбиениям</t>
+  </si>
+  <si>
+    <t>Влияние параметра eps в DBSCAN</t>
+  </si>
+  <si>
+    <t>Сравнение macro-F1 и weighted-F1</t>
+  </si>
+  <si>
+    <t>Применение Bernoulli Naive Bayes к бинаризованным признакам</t>
+  </si>
+  <si>
+    <t>Сравнение линейной модели и дерева на данных make_moons</t>
+  </si>
+  <si>
+    <t>Сравнение RobustScaler и StandardScaler при наличии выбросов</t>
+  </si>
+  <si>
+    <t>Классификация рукописных цифр методом ближайших соседей</t>
+  </si>
+  <si>
+    <t>Сравнение SGDClassifier и PassiveAggressiveClassifier</t>
+  </si>
+  <si>
+    <t>Построение Precision-Recall-кривой для редкого класса</t>
+  </si>
+  <si>
+    <t>Влияние дублирующихся строк на качество классификации</t>
+  </si>
+  <si>
+    <t>Влияние порога классификации 0,3; 0,5 и 0,7</t>
+  </si>
+  <si>
+    <t>Построение кривой обучения для классификатора</t>
+  </si>
+  <si>
+    <t>Сравнение униграмм и биграмм при классификации текстов</t>
+  </si>
+  <si>
+    <t>Влияние StandardScaler на логистическую регрессию</t>
+  </si>
+  <si>
+    <t>Добавление полиномиальных признаков для нелинейной зависимости</t>
+  </si>
+  <si>
+    <t>Случайное уменьшение объектов частого класса</t>
+  </si>
+  <si>
+    <t>Сравнение accuracy и F1 при дисбалансе классов</t>
+  </si>
+  <si>
+    <t>Сравнение вариантов linkage в AgglomerativeClustering</t>
+  </si>
+  <si>
+    <t>Сравнение MAE и RMSE при появлении выбросов</t>
+  </si>
+  <si>
+    <t>Классификация рукописных цифр простой линейной моделью</t>
+  </si>
+  <si>
+    <t>Влияние числа моделей в GradientBoostingClassifier</t>
+  </si>
+  <si>
+    <t>Влияние числа соседей в Local Outlier Factor</t>
+  </si>
+  <si>
+    <t>Прогноз следующего значения по лаговым признакам</t>
+  </si>
+  <si>
+    <t>Интерпретация коэффициентов линейной регрессии</t>
+  </si>
+  <si>
+    <t>Анализ нескольких ошибочно классифицированных объектов</t>
+  </si>
+  <si>
+    <t>Влияние параметра C в SVC</t>
+  </si>
+  <si>
+    <t>Влияние reg_param в QuadraticDiscriminantAnalysis</t>
+  </si>
+  <si>
+    <t>Определение языка короткого текста по символьным n-граммам</t>
+  </si>
+  <si>
+    <t>Сравнение весов классов и обычного обучения</t>
+  </si>
+  <si>
+    <t>Влияние min_samples в DBSCAN</t>
+  </si>
+  <si>
+    <t>Сравнение манхэттенского и евклидова расстояния в KNN</t>
+  </si>
+  <si>
+    <t>Влияние random_state при разбиении данных на результат модели</t>
+  </si>
+  <si>
+    <t>Упрощение дерева решений с помощью ccp_alpha</t>
+  </si>
+  <si>
+    <t>Влияние размера окна скользящего среднего</t>
+  </si>
+  <si>
+    <t>Построение Pipeline из масштабирования и классификатора</t>
+  </si>
+  <si>
+    <t>Влияние var_smoothing в Gaussian Naive Bayes</t>
+  </si>
+  <si>
+    <t>Добавление признака взаимодействия двух переменных</t>
+  </si>
+  <si>
+    <t>Влияние числа деревьев в Random Forest</t>
+  </si>
+  <si>
+    <t>Сохранение и загрузка обученной модели с помощью joblib</t>
+  </si>
+  <si>
+    <t>Влияние начальной инициализации центров в KMeans</t>
+  </si>
+  <si>
+    <t>Интерпретация коэффициента R² и графика остатков</t>
+  </si>
+  <si>
+    <t>Влияние доли пропусков на качество классификатора</t>
+  </si>
+  <si>
+    <t>Зависимость объяснённой дисперсии от числа компонент PCA</t>
+  </si>
+  <si>
+    <t>Восстановление изображений после сжатия методом PCA</t>
+  </si>
+  <si>
+    <t>Сравнение модели с DummyClassifier</t>
+  </si>
+  <si>
+    <t>Влияние contamination в Isolation Forest</t>
+  </si>
+  <si>
+    <t>Сравнение уверенности модели в правильных и ошибочных ответах</t>
+  </si>
+  <si>
+    <t>Влияние max_features в Random Forest</t>
+  </si>
+  <si>
+    <t>Влияние числа признаков в SelectKBest на качество модели</t>
+  </si>
+  <si>
+    <t>Сравнение трёхблочной и десятиблочной кросс-валидации</t>
+  </si>
+  <si>
+    <t>Применение ColumnTransformer к числовым и категориальным признакам</t>
+  </si>
+  <si>
+    <t>Влияние случайных шумовых признаков на качество модели</t>
+  </si>
+  <si>
+    <t>Влияние числа базовых моделей в BaggingClassifier</t>
+  </si>
+  <si>
+    <t>Обработка неизвестной категории с помощью OneHotEncoder</t>
+  </si>
+  <si>
+    <t>Влияние коэффициента alpha в Ridge-регрессии</t>
+  </si>
+  <si>
+    <t>Влияние разбиения числового признака на интервалы на классификацию</t>
+  </si>
+  <si>
+    <t>Заполнение категориальных пропусков самым частым значением и отдельной меткой</t>
+  </si>
+  <si>
+    <t>Подбор одного гиперпараметра с помощью GridSearchCV</t>
+  </si>
+  <si>
+    <t>Влияние параметра C в логистической регрессии</t>
+  </si>
+  <si>
+    <t>Сравнение Ridge и Lasso на одном наборе данных</t>
+  </si>
+  <si>
+    <t>Влияние числа итераций в SGDClassifier</t>
+  </si>
+  <si>
+    <t>Влияние числа соседей в KNeighborsClassifier</t>
+  </si>
+  <si>
+    <t>Влияние глубины дерева решений на переобучение</t>
+  </si>
+  <si>
+    <t>Сравнение Brier score двух классификаторов</t>
+  </si>
+  <si>
+    <t>Сравнение времени предсказания двух простых моделей</t>
+  </si>
+  <si>
+    <t>Сравнение калибровочных кривых двух классификаторов</t>
+  </si>
+  <si>
+    <t>Влияние perplexity на двумерную визуализацию t-SNE</t>
+  </si>
+  <si>
+    <t>Сравнение ExtraTrees и Random Forest</t>
+  </si>
+  <si>
+    <t>Сравнение случайного и хронологического разбиения временного ряда</t>
+  </si>
+  <si>
+    <t>Исследование компромисса между precision и recall</t>
+  </si>
+  <si>
+    <t>Подбор числа кластеров методом локтя</t>
+  </si>
+  <si>
+    <t>Демонстрация утечки данных при масштабировании до разбиения выборки</t>
+  </si>
+  <si>
+    <t>Влияние мультиколлинеарности на коэффициенты линейной регрессии</t>
+  </si>
+  <si>
+    <t>Удаление признаков с нулевой дисперсией с помощью VarianceThreshold</t>
+  </si>
+  <si>
+    <t>Влияние числа моделей в AdaBoostClassifier</t>
+  </si>
+  <si>
+    <t>Классификация методом ближайшего центроида</t>
+  </si>
+  <si>
+    <t>Влияние разделимости классов в make_classification</t>
   </si>
 </sst>
 </file>
@@ -639,19 +888,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K84"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:L84"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" customWidth="1"/>
-    <col min="2" max="2" width="31.28515625" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" customWidth="1"/>
-    <col min="5" max="5" width="70.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.5" customWidth="1"/>
+    <col min="2" max="2" width="31.33203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="77" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="70.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="12.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -662,31 +912,34 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H1" s="4">
+      <c r="I1" s="4">
         <v>46279</v>
       </c>
-      <c r="I1" s="4">
+      <c r="J1" s="4">
         <v>46286</v>
       </c>
-      <c r="J1" s="4">
+      <c r="K1" s="4">
         <v>46293</v>
       </c>
-      <c r="K1" s="4">
+      <c r="L1" s="4">
         <v>46300</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A2">
         <v>54</v>
       </c>
@@ -696,18 +949,21 @@
       <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E2">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>91</v>
       </c>
-      <c r="F2">
-        <f>SUM(G2:U2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G2">
+        <f>SUM(H2:V2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A3">
         <v>59</v>
       </c>
@@ -717,18 +973,21 @@
       <c r="C3" t="s">
         <v>5</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E3">
         <v>1</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>91</v>
       </c>
-      <c r="F3">
-        <f>SUM(G3:U3)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G3">
+        <f>SUM(H3:V3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A4">
         <v>51</v>
       </c>
@@ -738,25 +997,28 @@
       <c r="C4" t="s">
         <v>5</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E4">
         <v>2</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>92</v>
       </c>
-      <c r="F4">
-        <f>SUM(G4:U4)</f>
+      <c r="G4">
+        <f>SUM(H4:V4)</f>
         <v>6</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>2</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <f>2+2</f>
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A5">
         <v>66</v>
       </c>
@@ -766,18 +1028,21 @@
       <c r="C5" t="s">
         <v>5</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="s">
+        <v>138</v>
+      </c>
+      <c r="E5">
         <v>2</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>92</v>
       </c>
-      <c r="F5">
-        <f>SUM(G5:U5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G5">
+        <f>SUM(H5:V5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A6">
         <v>24</v>
       </c>
@@ -787,18 +1052,21 @@
       <c r="C6" t="s">
         <v>10</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="s">
+        <v>139</v>
+      </c>
+      <c r="E6">
         <v>3</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>93</v>
       </c>
-      <c r="F6">
-        <f>SUM(G6:U6)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G6">
+        <f>SUM(H6:V6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A7">
         <v>43</v>
       </c>
@@ -808,18 +1076,21 @@
       <c r="C7" t="s">
         <v>10</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="s">
+        <v>140</v>
+      </c>
+      <c r="E7">
         <v>3</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>93</v>
       </c>
-      <c r="F7">
-        <f>SUM(G7:U7)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G7">
+        <f>SUM(H7:V7)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A8">
         <v>22</v>
       </c>
@@ -829,26 +1100,29 @@
       <c r="C8" t="s">
         <v>10</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="s">
+        <v>141</v>
+      </c>
+      <c r="E8">
         <v>4</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>94</v>
       </c>
-      <c r="F8">
-        <f>SUM(G8:U8)</f>
+      <c r="G8">
+        <f>SUM(H8:V8)</f>
         <v>53</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>50</v>
       </c>
-      <c r="H8" s="2"/>
-      <c r="J8" s="2">
+      <c r="I8" s="2"/>
+      <c r="K8" s="2">
         <f>2+1+0</f>
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A9">
         <v>28</v>
       </c>
@@ -858,29 +1132,32 @@
       <c r="C9" t="s">
         <v>10</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="s">
+        <v>142</v>
+      </c>
+      <c r="E9">
         <v>4</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>94</v>
       </c>
-      <c r="F9">
-        <f>SUM(G9:U9)</f>
+      <c r="G9">
+        <f>SUM(H9:V9)</f>
         <v>57</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>50</v>
       </c>
-      <c r="H9" s="2"/>
-      <c r="I9">
+      <c r="I9" s="2"/>
+      <c r="J9">
         <v>1</v>
       </c>
-      <c r="J9" s="2">
+      <c r="K9" s="2">
         <f>2+2+2</f>
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A10">
         <v>9</v>
       </c>
@@ -890,36 +1167,39 @@
       <c r="C10" t="s">
         <v>15</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="s">
+        <v>143</v>
+      </c>
+      <c r="E10">
         <v>5</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>95</v>
       </c>
-      <c r="F10">
-        <f>SUM(G10:U10)</f>
+      <c r="G10">
+        <f>SUM(H10:V10)</f>
         <v>58</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>50</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="I10" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <f>1+1+1</f>
         <v>3</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <f>2</f>
         <v>2</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <f>1+0+2</f>
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A11">
         <v>21</v>
       </c>
@@ -929,32 +1209,35 @@
       <c r="C11" t="s">
         <v>15</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="s">
+        <v>144</v>
+      </c>
+      <c r="E11">
         <v>5</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>95</v>
       </c>
-      <c r="F11">
-        <f>SUM(G11:U11)</f>
+      <c r="G11">
+        <f>SUM(H11:V11)</f>
         <v>56</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>50</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="I11" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <f>1+1+1</f>
         <v>3</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <f>2+1</f>
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A12">
         <v>4</v>
       </c>
@@ -964,36 +1247,39 @@
       <c r="C12" t="s">
         <v>15</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="s">
+        <v>145</v>
+      </c>
+      <c r="E12">
         <v>6</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>96</v>
       </c>
-      <c r="F12">
-        <f>SUM(G12:U12)</f>
+      <c r="G12">
+        <f>SUM(H12:V12)</f>
         <v>54</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>50</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <f>1+1</f>
         <v>2</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="J12" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <f>2</f>
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A13">
         <v>17</v>
       </c>
@@ -1003,32 +1289,35 @@
       <c r="C13" t="s">
         <v>15</v>
       </c>
-      <c r="D13">
+      <c r="D13" t="s">
+        <v>146</v>
+      </c>
+      <c r="E13">
         <v>6</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>96</v>
       </c>
-      <c r="F13">
-        <f>SUM(G13:U13)</f>
+      <c r="G13">
+        <f>SUM(H13:V13)</f>
         <v>56</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>50</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="J13" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <f>2</f>
         <v>2</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <f>1+2+1</f>
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A14">
         <v>56</v>
       </c>
@@ -1038,18 +1327,21 @@
       <c r="C14" t="s">
         <v>5</v>
       </c>
-      <c r="D14">
+      <c r="D14" t="s">
+        <v>147</v>
+      </c>
+      <c r="E14">
         <v>7</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>97</v>
       </c>
-      <c r="F14">
-        <f>SUM(G14:U14)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G14">
+        <f>SUM(H14:V14)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A15">
         <v>68</v>
       </c>
@@ -1059,18 +1351,21 @@
       <c r="C15" t="s">
         <v>5</v>
       </c>
-      <c r="D15">
+      <c r="D15" t="s">
+        <v>148</v>
+      </c>
+      <c r="E15">
         <v>7</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>97</v>
       </c>
-      <c r="F15">
-        <f>SUM(G15:U15)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G15">
+        <f>SUM(H15:V15)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A16">
         <v>48</v>
       </c>
@@ -1080,32 +1375,35 @@
       <c r="C16" t="s">
         <v>5</v>
       </c>
-      <c r="D16">
+      <c r="D16" t="s">
+        <v>149</v>
+      </c>
+      <c r="E16">
         <v>8</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>98</v>
       </c>
-      <c r="F16">
-        <f>SUM(G16:U16)</f>
+      <c r="G16">
+        <f>SUM(H16:V16)</f>
         <v>53</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>50</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <f>2</f>
         <v>2</v>
       </c>
-      <c r="I16" s="2" t="s">
+      <c r="J16" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <f>1</f>
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A17">
         <v>67</v>
       </c>
@@ -1115,29 +1413,32 @@
       <c r="C17" t="s">
         <v>5</v>
       </c>
-      <c r="D17">
+      <c r="D17" t="s">
+        <v>150</v>
+      </c>
+      <c r="E17">
         <v>8</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>98</v>
       </c>
-      <c r="F17">
-        <f>SUM(G17:U17)</f>
+      <c r="G17">
+        <f>SUM(H17:V17)</f>
         <v>56</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>50</v>
       </c>
-      <c r="I17" s="2">
+      <c r="J17" s="2">
         <f>2</f>
         <v>2</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <f>1+2+1</f>
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A18">
         <v>46</v>
       </c>
@@ -1147,18 +1448,21 @@
       <c r="C18" t="s">
         <v>5</v>
       </c>
-      <c r="D18">
+      <c r="D18" t="s">
+        <v>151</v>
+      </c>
+      <c r="E18">
         <v>9</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>99</v>
       </c>
-      <c r="F18">
-        <f>SUM(G18:U18)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G18">
+        <f>SUM(H18:V18)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A19">
         <v>65</v>
       </c>
@@ -1168,26 +1472,29 @@
       <c r="C19" t="s">
         <v>5</v>
       </c>
-      <c r="D19">
+      <c r="D19" t="s">
+        <v>152</v>
+      </c>
+      <c r="E19">
         <v>9</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>99</v>
       </c>
-      <c r="F19" s="5">
-        <f>SUM(G19:U19)</f>
+      <c r="G19" s="5">
+        <f>SUM(H19:V19)</f>
         <v>10</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <f>1+2+1</f>
         <v>4</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <f>2+2+1+1</f>
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A20">
         <v>2</v>
       </c>
@@ -1197,34 +1504,37 @@
       <c r="C20" t="s">
         <v>15</v>
       </c>
-      <c r="D20">
+      <c r="D20" t="s">
+        <v>153</v>
+      </c>
+      <c r="E20">
         <v>10</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>100</v>
       </c>
-      <c r="F20" s="5">
-        <f>SUM(G20:U20)</f>
+      <c r="G20" s="5">
+        <f>SUM(H20:V20)</f>
         <v>10</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <f>1+1</f>
         <v>2</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <f>2+1+2</f>
         <v>5</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <f>1+1</f>
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A21">
         <v>38</v>
       </c>
@@ -1234,26 +1544,29 @@
       <c r="C21" t="s">
         <v>10</v>
       </c>
-      <c r="D21">
+      <c r="D21" t="s">
+        <v>154</v>
+      </c>
+      <c r="E21">
         <v>10</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>100</v>
       </c>
-      <c r="F21">
-        <f>SUM(G21:U21)</f>
+      <c r="G21">
+        <f>SUM(H21:V21)</f>
         <v>5</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <f>1+2</f>
         <v>3</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <f>2</f>
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A22">
         <v>7</v>
       </c>
@@ -1263,18 +1576,21 @@
       <c r="C22" t="s">
         <v>15</v>
       </c>
-      <c r="D22">
+      <c r="D22" t="s">
+        <v>155</v>
+      </c>
+      <c r="E22">
         <v>11</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>101</v>
       </c>
-      <c r="F22">
-        <f>SUM(G22:U22)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G22">
+        <f>SUM(H22:V22)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A23">
         <v>18</v>
       </c>
@@ -1284,22 +1600,25 @@
       <c r="C23" t="s">
         <v>15</v>
       </c>
-      <c r="D23">
+      <c r="D23" t="s">
+        <v>156</v>
+      </c>
+      <c r="E23">
         <v>11</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>101</v>
       </c>
-      <c r="F23">
-        <f>SUM(G23:U23)</f>
+      <c r="G23">
+        <f>SUM(H23:V23)</f>
         <v>1</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <f>1</f>
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A24">
         <v>13</v>
       </c>
@@ -1309,30 +1628,33 @@
       <c r="C24" t="s">
         <v>15</v>
       </c>
-      <c r="D24">
+      <c r="D24" t="s">
+        <v>157</v>
+      </c>
+      <c r="E24">
         <v>12</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>102</v>
       </c>
-      <c r="F24" s="5">
-        <f>SUM(G24:U24)</f>
+      <c r="G24" s="5">
+        <f>SUM(H24:V24)</f>
         <v>10</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="I24">
+      <c r="J24">
         <f>1+1+1</f>
         <v>3</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <f>2+2+2</f>
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A25">
         <v>19</v>
       </c>
@@ -1342,22 +1664,25 @@
       <c r="C25" t="s">
         <v>15</v>
       </c>
-      <c r="D25">
+      <c r="D25" t="s">
+        <v>158</v>
+      </c>
+      <c r="E25">
         <v>12</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>102</v>
       </c>
-      <c r="F25">
-        <f>SUM(G25:U25)</f>
+      <c r="G25">
+        <f>SUM(H25:V25)</f>
         <v>1</v>
       </c>
-      <c r="H25">
+      <c r="I25">
         <f>1</f>
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A26">
         <v>73</v>
       </c>
@@ -1367,33 +1692,36 @@
       <c r="C26" t="s">
         <v>32</v>
       </c>
-      <c r="D26">
+      <c r="D26" t="s">
+        <v>159</v>
+      </c>
+      <c r="E26">
         <v>13</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>103</v>
       </c>
-      <c r="F26">
-        <f>SUM(G26:U26)</f>
+      <c r="G26">
+        <f>SUM(H26:V26)</f>
         <v>55</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>50</v>
       </c>
-      <c r="I26" s="2">
+      <c r="J26" s="2">
         <f>1+1</f>
         <v>2</v>
       </c>
-      <c r="J26">
+      <c r="K26">
         <f>2</f>
         <v>2</v>
       </c>
-      <c r="K26">
+      <c r="L26">
         <f>1</f>
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A27">
         <v>76</v>
       </c>
@@ -1403,36 +1731,39 @@
       <c r="C27" t="s">
         <v>32</v>
       </c>
-      <c r="D27">
+      <c r="D27" t="s">
+        <v>160</v>
+      </c>
+      <c r="E27">
         <v>13</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>103</v>
       </c>
-      <c r="F27">
-        <f>SUM(G27:U27)</f>
+      <c r="G27">
+        <f>SUM(H27:V27)</f>
         <v>58</v>
       </c>
-      <c r="G27">
+      <c r="H27">
         <v>50</v>
       </c>
-      <c r="H27">
+      <c r="I27">
         <f>1+1</f>
         <v>2</v>
       </c>
-      <c r="I27" s="2" t="s">
+      <c r="J27" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="J27">
+      <c r="K27">
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="K27">
+      <c r="L27">
         <f>2+1+0+2</f>
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A28">
         <v>53</v>
       </c>
@@ -1442,18 +1773,21 @@
       <c r="C28" t="s">
         <v>5</v>
       </c>
-      <c r="D28">
+      <c r="D28" t="s">
+        <v>161</v>
+      </c>
+      <c r="E28">
         <v>14</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>104</v>
       </c>
-      <c r="F28">
-        <f>SUM(G28:U28)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G28">
+        <f>SUM(H28:V28)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A29">
         <v>60</v>
       </c>
@@ -1463,18 +1797,21 @@
       <c r="C29" t="s">
         <v>5</v>
       </c>
-      <c r="D29">
+      <c r="D29" t="s">
+        <v>162</v>
+      </c>
+      <c r="E29">
         <v>14</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>104</v>
       </c>
-      <c r="F29">
-        <f>SUM(G29:U29)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G29">
+        <f>SUM(H29:V29)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A30">
         <v>6</v>
       </c>
@@ -1484,18 +1821,21 @@
       <c r="C30" t="s">
         <v>15</v>
       </c>
-      <c r="D30">
+      <c r="D30" t="s">
+        <v>163</v>
+      </c>
+      <c r="E30">
         <v>15</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>105</v>
       </c>
-      <c r="F30">
-        <f>SUM(G30:U30)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G30">
+        <f>SUM(H30:V30)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A31">
         <v>20</v>
       </c>
@@ -1505,18 +1845,21 @@
       <c r="C31" t="s">
         <v>15</v>
       </c>
-      <c r="D31">
+      <c r="D31" t="s">
+        <v>164</v>
+      </c>
+      <c r="E31">
         <v>15</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>105</v>
       </c>
-      <c r="F31">
-        <f>SUM(G31:U31)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G31">
+        <f>SUM(H31:V31)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A32">
         <v>52</v>
       </c>
@@ -1526,24 +1869,27 @@
       <c r="C32" t="s">
         <v>5</v>
       </c>
-      <c r="D32">
+      <c r="D32" t="s">
+        <v>165</v>
+      </c>
+      <c r="E32">
         <v>16</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>106</v>
       </c>
-      <c r="F32">
-        <f>SUM(G32:U32)</f>
+      <c r="G32">
+        <f>SUM(H32:V32)</f>
         <v>50</v>
       </c>
-      <c r="G32">
+      <c r="H32">
         <v>50</v>
       </c>
-      <c r="K32" s="2" t="s">
+      <c r="L32" s="2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A33">
         <v>55</v>
       </c>
@@ -1553,29 +1899,32 @@
       <c r="C33" t="s">
         <v>5</v>
       </c>
-      <c r="D33">
+      <c r="D33" t="s">
+        <v>166</v>
+      </c>
+      <c r="E33">
         <v>16</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>106</v>
       </c>
-      <c r="F33">
-        <f>SUM(G33:U33)</f>
+      <c r="G33">
+        <f>SUM(H33:V33)</f>
         <v>56</v>
       </c>
-      <c r="G33">
+      <c r="H33">
         <v>50</v>
       </c>
-      <c r="J33">
+      <c r="K33">
         <f>2+1</f>
         <v>3</v>
       </c>
-      <c r="K33" s="2">
+      <c r="L33" s="2">
         <f>1+2</f>
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A34">
         <v>36</v>
       </c>
@@ -1585,22 +1934,25 @@
       <c r="C34" t="s">
         <v>10</v>
       </c>
-      <c r="D34">
+      <c r="D34" t="s">
+        <v>167</v>
+      </c>
+      <c r="E34">
         <v>17</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>107</v>
       </c>
-      <c r="F34">
-        <f>SUM(G34:U34)</f>
+      <c r="G34">
+        <f>SUM(H34:V34)</f>
         <v>1</v>
       </c>
-      <c r="K34">
+      <c r="L34">
         <f>1</f>
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A35">
         <v>39</v>
       </c>
@@ -1610,26 +1962,29 @@
       <c r="C35" t="s">
         <v>10</v>
       </c>
-      <c r="D35">
+      <c r="D35" t="s">
+        <v>168</v>
+      </c>
+      <c r="E35">
         <v>17</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>107</v>
       </c>
-      <c r="F35">
-        <f>SUM(G35:U35)</f>
+      <c r="G35">
+        <f>SUM(H35:V35)</f>
         <v>4</v>
-      </c>
-      <c r="J35">
-        <f>2</f>
-        <v>2</v>
       </c>
       <c r="K35">
         <f>2</f>
         <v>2</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L35">
+        <f>2</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A36">
         <v>45</v>
       </c>
@@ -1639,18 +1994,21 @@
       <c r="C36" t="s">
         <v>5</v>
       </c>
-      <c r="D36">
+      <c r="D36" t="s">
+        <v>169</v>
+      </c>
+      <c r="E36">
         <v>18</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>108</v>
       </c>
-      <c r="F36">
-        <f>SUM(G36:U36)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G36">
+        <f>SUM(H36:V36)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A37">
         <v>64</v>
       </c>
@@ -1660,18 +2018,21 @@
       <c r="C37" t="s">
         <v>5</v>
       </c>
-      <c r="D37">
+      <c r="D37" t="s">
+        <v>170</v>
+      </c>
+      <c r="E37">
         <v>18</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>108</v>
       </c>
-      <c r="F37">
-        <f>SUM(G37:U37)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G37">
+        <f>SUM(H37:V37)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A38">
         <v>29</v>
       </c>
@@ -1681,18 +2042,21 @@
       <c r="C38" t="s">
         <v>10</v>
       </c>
-      <c r="D38">
+      <c r="D38" t="s">
+        <v>171</v>
+      </c>
+      <c r="E38">
         <v>19</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>109</v>
       </c>
-      <c r="F38">
-        <f>SUM(G38:U38)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G38">
+        <f>SUM(H38:V38)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A39">
         <v>42</v>
       </c>
@@ -1702,18 +2066,21 @@
       <c r="C39" t="s">
         <v>10</v>
       </c>
-      <c r="D39">
+      <c r="D39" t="s">
+        <v>172</v>
+      </c>
+      <c r="E39">
         <v>19</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>109</v>
       </c>
-      <c r="F39">
-        <f>SUM(G39:U39)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G39">
+        <f>SUM(H39:V39)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A40">
         <v>1</v>
       </c>
@@ -1723,28 +2090,31 @@
       <c r="C40" t="s">
         <v>15</v>
       </c>
-      <c r="D40">
+      <c r="D40" t="s">
+        <v>173</v>
+      </c>
+      <c r="E40">
         <v>20</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>110</v>
       </c>
-      <c r="F40">
-        <f>SUM(G40:U40)</f>
+      <c r="G40">
+        <f>SUM(H40:V40)</f>
         <v>52</v>
       </c>
-      <c r="G40">
+      <c r="H40">
         <v>50</v>
       </c>
-      <c r="H40" s="2" t="s">
+      <c r="I40" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="K40">
+      <c r="L40">
         <f>1+1</f>
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A41">
         <v>5</v>
       </c>
@@ -1754,90 +2124,99 @@
       <c r="C41" t="s">
         <v>15</v>
       </c>
-      <c r="D41">
+      <c r="D41" t="s">
+        <v>174</v>
+      </c>
+      <c r="E41">
         <v>20</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>110</v>
       </c>
-      <c r="F41" s="5">
-        <f>SUM(G41:U41)</f>
+      <c r="G41" s="5">
+        <f>SUM(H41:V41)</f>
         <v>60</v>
       </c>
-      <c r="G41">
+      <c r="H41">
         <v>50</v>
       </c>
-      <c r="H41" s="2">
+      <c r="I41" s="2">
         <v>1</v>
       </c>
-      <c r="K41">
+      <c r="L41">
         <f>2+2+2+2+1</f>
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A42">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="C42" t="s">
-        <v>32</v>
-      </c>
-      <c r="D42">
+        <v>15</v>
+      </c>
+      <c r="D42" t="s">
+        <v>175</v>
+      </c>
+      <c r="E42">
         <v>21</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>111</v>
       </c>
-      <c r="F42">
-        <f>SUM(G42:U42)</f>
-        <v>52</v>
-      </c>
       <c r="G42">
+        <f>SUM(H42:V42)</f>
+        <v>55</v>
+      </c>
+      <c r="H42">
         <v>50</v>
       </c>
-      <c r="H42" s="2"/>
-      <c r="K42" s="2">
+      <c r="I42" s="2"/>
+      <c r="J42">
         <f>2</f>
         <v>2</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="2">
+        <f>2+1</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A43">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="C43" t="s">
-        <v>15</v>
-      </c>
-      <c r="D43">
+        <v>32</v>
+      </c>
+      <c r="D43" t="s">
+        <v>176</v>
+      </c>
+      <c r="E43">
         <v>21</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>111</v>
       </c>
-      <c r="F43">
-        <f>SUM(G43:U43)</f>
-        <v>55</v>
-      </c>
       <c r="G43">
+        <f>SUM(H43:V43)</f>
+        <v>52</v>
+      </c>
+      <c r="H43">
         <v>50</v>
       </c>
-      <c r="H43" s="2"/>
-      <c r="I43">
+      <c r="I43" s="2"/>
+      <c r="L43" s="2">
         <f>2</f>
         <v>2</v>
       </c>
-      <c r="K43" s="2">
-        <f>2+1</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A44">
         <v>26</v>
       </c>
@@ -1847,30 +2226,33 @@
       <c r="C44" t="s">
         <v>10</v>
       </c>
-      <c r="D44">
+      <c r="D44" t="s">
+        <v>177</v>
+      </c>
+      <c r="E44">
         <v>22</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>112</v>
       </c>
-      <c r="F44">
-        <f>SUM(G44:U44)</f>
+      <c r="G44">
+        <f>SUM(H44:V44)</f>
         <v>4</v>
       </c>
-      <c r="I44">
+      <c r="J44">
         <f>2</f>
         <v>2</v>
-      </c>
-      <c r="J44">
-        <f>1</f>
-        <v>1</v>
       </c>
       <c r="K44">
         <f>1</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L44">
+        <f>1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A45">
         <v>31</v>
       </c>
@@ -1880,60 +2262,69 @@
       <c r="C45" t="s">
         <v>10</v>
       </c>
-      <c r="D45">
+      <c r="D45" t="s">
+        <v>178</v>
+      </c>
+      <c r="E45">
         <v>22</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>112</v>
       </c>
-      <c r="F45">
-        <f>SUM(G45:U45)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G45">
+        <f>SUM(H45:V45)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A46">
+        <v>14</v>
+      </c>
+      <c r="B46" t="s">
+        <v>49</v>
+      </c>
+      <c r="C46" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46" t="s">
+        <v>179</v>
+      </c>
+      <c r="E46">
+        <v>23</v>
+      </c>
+      <c r="F46" t="s">
+        <v>113</v>
+      </c>
+      <c r="G46">
+        <f>SUM(H46:V46)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A47">
         <v>72</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B47" t="s">
         <v>81</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C47" t="s">
         <v>32</v>
       </c>
-      <c r="D46">
+      <c r="D47" t="s">
+        <v>180</v>
+      </c>
+      <c r="E47">
         <v>23</v>
       </c>
-      <c r="E46" t="s">
+      <c r="F47" t="s">
         <v>113</v>
       </c>
-      <c r="F46">
-        <f>SUM(G46:U46)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A47">
-        <v>14</v>
-      </c>
-      <c r="B47" t="s">
-        <v>49</v>
-      </c>
-      <c r="C47" t="s">
-        <v>15</v>
-      </c>
-      <c r="D47">
-        <v>23</v>
-      </c>
-      <c r="E47" t="s">
-        <v>113</v>
-      </c>
-      <c r="F47">
-        <f>SUM(G47:U47)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G47">
+        <f>SUM(H47:V47)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A48">
         <v>49</v>
       </c>
@@ -1943,18 +2334,21 @@
       <c r="C48" t="s">
         <v>5</v>
       </c>
-      <c r="D48">
+      <c r="D48" t="s">
+        <v>181</v>
+      </c>
+      <c r="E48">
         <v>24</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
         <v>115</v>
       </c>
-      <c r="F48">
-        <f>SUM(G48:U48)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G48">
+        <f>SUM(H48:V48)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A49">
         <v>58</v>
       </c>
@@ -1964,22 +2358,25 @@
       <c r="C49" t="s">
         <v>5</v>
       </c>
-      <c r="D49">
+      <c r="D49" t="s">
+        <v>182</v>
+      </c>
+      <c r="E49">
         <v>24</v>
       </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
         <v>115</v>
       </c>
-      <c r="F49">
-        <f>SUM(G49:U49)</f>
+      <c r="G49">
+        <f>SUM(H49:V49)</f>
         <v>1</v>
       </c>
-      <c r="I49">
+      <c r="J49">
         <f>1</f>
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A50">
         <v>50</v>
       </c>
@@ -1989,18 +2386,21 @@
       <c r="C50" t="s">
         <v>5</v>
       </c>
-      <c r="D50">
+      <c r="D50" t="s">
+        <v>183</v>
+      </c>
+      <c r="E50">
         <v>25</v>
       </c>
-      <c r="E50" t="s">
+      <c r="F50" t="s">
         <v>116</v>
       </c>
-      <c r="F50">
-        <f>SUM(G50:U50)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G50">
+        <f>SUM(H50:V50)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A51">
         <v>75</v>
       </c>
@@ -2010,18 +2410,21 @@
       <c r="C51" t="s">
         <v>32</v>
       </c>
-      <c r="D51">
+      <c r="D51" t="s">
+        <v>184</v>
+      </c>
+      <c r="E51">
         <v>25</v>
       </c>
-      <c r="E51" t="s">
+      <c r="F51" t="s">
         <v>116</v>
       </c>
-      <c r="F51">
-        <f>SUM(G51:U51)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G51">
+        <f>SUM(H51:V51)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A52">
         <v>34</v>
       </c>
@@ -2031,29 +2434,32 @@
       <c r="C52" t="s">
         <v>10</v>
       </c>
-      <c r="D52">
+      <c r="D52" t="s">
+        <v>185</v>
+      </c>
+      <c r="E52">
         <v>26</v>
       </c>
-      <c r="E52" t="s">
+      <c r="F52" t="s">
         <v>117</v>
       </c>
-      <c r="F52">
-        <f>SUM(G52:U52)</f>
+      <c r="G52">
+        <f>SUM(H52:V52)</f>
         <v>58</v>
       </c>
-      <c r="G52">
+      <c r="H52">
         <v>50</v>
       </c>
-      <c r="J52" s="2">
+      <c r="K52" s="2">
         <f>2+2+0+2</f>
         <v>6</v>
       </c>
-      <c r="K52">
+      <c r="L52">
         <f>2</f>
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A53">
         <v>41</v>
       </c>
@@ -2063,25 +2469,28 @@
       <c r="C53" t="s">
         <v>10</v>
       </c>
-      <c r="D53">
+      <c r="D53" t="s">
+        <v>186</v>
+      </c>
+      <c r="E53">
         <v>26</v>
       </c>
-      <c r="E53" t="s">
+      <c r="F53" t="s">
         <v>117</v>
       </c>
-      <c r="F53">
-        <f>SUM(G53:U53)</f>
+      <c r="G53">
+        <f>SUM(H53:V53)</f>
         <v>53</v>
       </c>
-      <c r="G53">
+      <c r="H53">
         <v>50</v>
       </c>
-      <c r="J53" s="2">
+      <c r="K53" s="2">
         <f>1+0+2+0</f>
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A54">
         <v>77</v>
       </c>
@@ -2091,18 +2500,21 @@
       <c r="C54" t="s">
         <v>32</v>
       </c>
-      <c r="D54">
+      <c r="D54" t="s">
+        <v>187</v>
+      </c>
+      <c r="E54">
         <v>27</v>
       </c>
-      <c r="E54" t="s">
+      <c r="F54" t="s">
         <v>118</v>
       </c>
-      <c r="F54">
-        <f>SUM(G54:U54)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G54">
+        <f>SUM(H54:V54)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A55">
         <v>78</v>
       </c>
@@ -2112,18 +2524,21 @@
       <c r="C55" t="s">
         <v>32</v>
       </c>
-      <c r="D55">
+      <c r="D55" t="s">
+        <v>188</v>
+      </c>
+      <c r="E55">
         <v>27</v>
       </c>
-      <c r="E55" t="s">
+      <c r="F55" t="s">
         <v>118</v>
       </c>
-      <c r="F55">
-        <f>SUM(G55:U55)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G55">
+        <f>SUM(H55:V55)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A56">
         <v>30</v>
       </c>
@@ -2133,29 +2548,32 @@
       <c r="C56" t="s">
         <v>10</v>
       </c>
-      <c r="D56">
+      <c r="D56" t="s">
+        <v>189</v>
+      </c>
+      <c r="E56">
         <v>28</v>
       </c>
-      <c r="E56" t="s">
+      <c r="F56" t="s">
         <v>119</v>
       </c>
-      <c r="F56">
-        <f>SUM(G56:U56)</f>
+      <c r="G56">
+        <f>SUM(H56:V56)</f>
         <v>56</v>
       </c>
-      <c r="G56">
+      <c r="H56">
         <v>50</v>
       </c>
-      <c r="J56" s="2">
+      <c r="K56" s="2">
         <f>2+2+1</f>
         <v>5</v>
       </c>
-      <c r="K56">
+      <c r="L56">
         <f>1</f>
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A57">
         <v>40</v>
       </c>
@@ -2165,29 +2583,32 @@
       <c r="C57" t="s">
         <v>10</v>
       </c>
-      <c r="D57">
+      <c r="D57" t="s">
+        <v>190</v>
+      </c>
+      <c r="E57">
         <v>28</v>
       </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>119</v>
       </c>
-      <c r="F57">
-        <f>SUM(G57:U57)</f>
+      <c r="G57">
+        <f>SUM(H57:V57)</f>
         <v>57</v>
       </c>
-      <c r="G57">
+      <c r="H57">
         <v>50</v>
       </c>
-      <c r="J57" s="2">
+      <c r="K57" s="2">
         <f>2+2+1</f>
         <v>5</v>
       </c>
-      <c r="K57">
+      <c r="L57">
         <f>1+1</f>
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A58">
         <v>3</v>
       </c>
@@ -2197,18 +2618,21 @@
       <c r="C58" t="s">
         <v>15</v>
       </c>
-      <c r="D58">
+      <c r="D58" t="s">
+        <v>191</v>
+      </c>
+      <c r="E58">
         <v>29</v>
       </c>
-      <c r="E58" t="s">
+      <c r="F58" t="s">
         <v>120</v>
       </c>
-      <c r="F58">
-        <f>SUM(G58:U58)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G58">
+        <f>SUM(H58:V58)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A59">
         <v>10</v>
       </c>
@@ -2218,18 +2642,21 @@
       <c r="C59" t="s">
         <v>15</v>
       </c>
-      <c r="D59">
+      <c r="D59" t="s">
+        <v>192</v>
+      </c>
+      <c r="E59">
         <v>29</v>
       </c>
-      <c r="E59" t="s">
+      <c r="F59" t="s">
         <v>120</v>
       </c>
-      <c r="F59">
-        <f>SUM(G59:U59)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G59">
+        <f>SUM(H59:V59)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A60">
         <v>23</v>
       </c>
@@ -2239,22 +2666,25 @@
       <c r="C60" t="s">
         <v>10</v>
       </c>
-      <c r="D60">
+      <c r="D60" t="s">
+        <v>193</v>
+      </c>
+      <c r="E60">
         <v>30</v>
       </c>
-      <c r="E60" t="s">
+      <c r="F60" t="s">
         <v>121</v>
       </c>
-      <c r="F60">
-        <f>SUM(G60:U60)</f>
+      <c r="G60">
+        <f>SUM(H60:V60)</f>
         <v>1</v>
       </c>
-      <c r="K60">
+      <c r="L60">
         <f>0+1</f>
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A61">
         <v>35</v>
       </c>
@@ -2264,18 +2694,21 @@
       <c r="C61" t="s">
         <v>10</v>
       </c>
-      <c r="D61">
+      <c r="D61" t="s">
+        <v>194</v>
+      </c>
+      <c r="E61">
         <v>30</v>
       </c>
-      <c r="E61" t="s">
+      <c r="F61" t="s">
         <v>121</v>
       </c>
-      <c r="F61">
-        <f>SUM(G61:U61)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G61">
+        <f>SUM(H61:V61)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A62">
         <v>62</v>
       </c>
@@ -2285,18 +2718,21 @@
       <c r="C62" t="s">
         <v>5</v>
       </c>
-      <c r="D62">
+      <c r="D62" t="s">
+        <v>195</v>
+      </c>
+      <c r="E62">
         <v>31</v>
       </c>
-      <c r="E62" t="s">
+      <c r="F62" t="s">
         <v>122</v>
       </c>
-      <c r="F62">
-        <f>SUM(G62:U62)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G62">
+        <f>SUM(H62:V62)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A63">
         <v>63</v>
       </c>
@@ -2306,18 +2742,21 @@
       <c r="C63" t="s">
         <v>5</v>
       </c>
-      <c r="D63">
+      <c r="D63" t="s">
+        <v>196</v>
+      </c>
+      <c r="E63">
         <v>31</v>
       </c>
-      <c r="E63" t="s">
+      <c r="F63" t="s">
         <v>122</v>
       </c>
-      <c r="F63">
-        <f>SUM(G63:U63)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G63">
+        <f>SUM(H63:V63)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A64">
         <v>27</v>
       </c>
@@ -2327,19 +2766,22 @@
       <c r="C64" t="s">
         <v>10</v>
       </c>
-      <c r="D64">
+      <c r="D64" t="s">
+        <v>197</v>
+      </c>
+      <c r="E64">
         <v>32</v>
       </c>
-      <c r="E64" t="s">
+      <c r="F64" t="s">
         <v>123</v>
       </c>
-      <c r="F64">
-        <f>SUM(G64:U64)</f>
-        <v>0</v>
-      </c>
-      <c r="I64" s="2"/>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G64">
+        <f>SUM(H64:V64)</f>
+        <v>0</v>
+      </c>
+      <c r="J64" s="2"/>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A65">
         <v>32</v>
       </c>
@@ -2349,22 +2791,25 @@
       <c r="C65" t="s">
         <v>10</v>
       </c>
-      <c r="D65">
+      <c r="D65" t="s">
+        <v>198</v>
+      </c>
+      <c r="E65">
         <v>32</v>
       </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
         <v>123</v>
       </c>
-      <c r="F65">
-        <f>SUM(G65:U65)</f>
+      <c r="G65">
+        <f>SUM(H65:V65)</f>
         <v>2</v>
       </c>
-      <c r="K65">
+      <c r="L65">
         <f>2</f>
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A66">
         <v>37</v>
       </c>
@@ -2374,18 +2819,21 @@
       <c r="C66" t="s">
         <v>10</v>
       </c>
-      <c r="D66">
+      <c r="D66" t="s">
+        <v>199</v>
+      </c>
+      <c r="E66">
         <v>33</v>
       </c>
-      <c r="E66" t="s">
+      <c r="F66" t="s">
         <v>125</v>
       </c>
-      <c r="F66">
-        <f>SUM(G66:U66)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G66">
+        <f>SUM(H66:V66)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A67">
         <v>44</v>
       </c>
@@ -2395,18 +2843,21 @@
       <c r="C67" t="s">
         <v>10</v>
       </c>
-      <c r="D67">
+      <c r="D67" t="s">
+        <v>200</v>
+      </c>
+      <c r="E67">
         <v>33</v>
       </c>
-      <c r="E67" t="s">
+      <c r="F67" t="s">
         <v>125</v>
       </c>
-      <c r="F67">
-        <f>SUM(G67:U67)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G67">
+        <f>SUM(H67:V67)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A68">
         <v>70</v>
       </c>
@@ -2416,18 +2867,21 @@
       <c r="C68" t="s">
         <v>32</v>
       </c>
-      <c r="D68">
+      <c r="D68" t="s">
+        <v>201</v>
+      </c>
+      <c r="E68">
         <v>34</v>
       </c>
-      <c r="E68" t="s">
+      <c r="F68" t="s">
         <v>124</v>
       </c>
-      <c r="F68">
-        <f>SUM(G68:U68)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G68">
+        <f>SUM(H68:V68)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A69">
         <v>79</v>
       </c>
@@ -2437,18 +2891,21 @@
       <c r="C69" t="s">
         <v>32</v>
       </c>
-      <c r="D69">
+      <c r="D69" t="s">
+        <v>202</v>
+      </c>
+      <c r="E69">
         <v>34</v>
       </c>
-      <c r="E69" t="s">
+      <c r="F69" t="s">
         <v>124</v>
       </c>
-      <c r="F69">
-        <f>SUM(G69:U69)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G69">
+        <f>SUM(H69:V69)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A70">
         <v>12</v>
       </c>
@@ -2458,18 +2915,21 @@
       <c r="C70" t="s">
         <v>15</v>
       </c>
-      <c r="D70">
+      <c r="D70" t="s">
+        <v>203</v>
+      </c>
+      <c r="E70">
         <v>35</v>
       </c>
-      <c r="E70" t="s">
+      <c r="F70" t="s">
         <v>128</v>
       </c>
-      <c r="F70">
-        <f>SUM(G70:U70)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G70">
+        <f>SUM(H70:V70)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A71">
         <v>16</v>
       </c>
@@ -2479,18 +2939,21 @@
       <c r="C71" t="s">
         <v>15</v>
       </c>
-      <c r="D71">
+      <c r="D71" t="s">
+        <v>204</v>
+      </c>
+      <c r="E71">
         <v>35</v>
       </c>
-      <c r="E71" t="s">
+      <c r="F71" t="s">
         <v>128</v>
       </c>
-      <c r="F71">
-        <f>SUM(G71:U71)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G71">
+        <f>SUM(H71:V71)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A72">
         <v>71</v>
       </c>
@@ -2500,36 +2963,39 @@
       <c r="C72" t="s">
         <v>32</v>
       </c>
-      <c r="D72">
+      <c r="D72" t="s">
+        <v>205</v>
+      </c>
+      <c r="E72">
         <v>36</v>
       </c>
-      <c r="E72" t="s">
+      <c r="F72" t="s">
         <v>126</v>
       </c>
-      <c r="F72" s="5">
-        <f>SUM(G72:U72)</f>
+      <c r="G72" s="5">
+        <f>SUM(H72:V72)</f>
         <v>60</v>
       </c>
-      <c r="G72">
+      <c r="H72">
         <v>50</v>
       </c>
-      <c r="H72">
+      <c r="I72">
         <f>1+1</f>
         <v>2</v>
       </c>
-      <c r="I72">
+      <c r="J72">
         <f>1+1+1+1</f>
         <v>4</v>
       </c>
-      <c r="J72">
+      <c r="K72">
         <f>2+1+1</f>
         <v>4</v>
       </c>
-      <c r="K72" s="2" t="s">
+      <c r="L72" s="2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A73">
         <v>74</v>
       </c>
@@ -2539,33 +3005,36 @@
       <c r="C73" t="s">
         <v>32</v>
       </c>
-      <c r="D73">
+      <c r="D73" t="s">
+        <v>206</v>
+      </c>
+      <c r="E73">
         <v>36</v>
       </c>
-      <c r="E73" t="s">
+      <c r="F73" t="s">
         <v>126</v>
       </c>
-      <c r="F73">
-        <f>SUM(G73:U73)</f>
+      <c r="G73">
+        <f>SUM(H73:V73)</f>
         <v>53</v>
       </c>
-      <c r="G73">
+      <c r="H73">
         <v>50</v>
-      </c>
-      <c r="H73">
-        <f>1</f>
-        <v>1</v>
       </c>
       <c r="I73">
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="K73" s="2">
+      <c r="J73">
         <f>1</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="2">
+        <f>1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A74">
         <v>80</v>
       </c>
@@ -2575,22 +3044,25 @@
       <c r="C74" t="s">
         <v>32</v>
       </c>
-      <c r="D74">
+      <c r="D74" t="s">
+        <v>207</v>
+      </c>
+      <c r="E74">
         <v>37</v>
       </c>
-      <c r="E74" t="s">
+      <c r="F74" t="s">
         <v>127</v>
       </c>
-      <c r="F74">
-        <f>SUM(G74:U74)</f>
+      <c r="G74">
+        <f>SUM(H74:V74)</f>
         <v>1</v>
       </c>
-      <c r="K74">
+      <c r="L74">
         <f>1</f>
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A75">
         <v>81</v>
       </c>
@@ -2600,22 +3072,25 @@
       <c r="C75" t="s">
         <v>32</v>
       </c>
-      <c r="D75">
+      <c r="D75" t="s">
+        <v>208</v>
+      </c>
+      <c r="E75">
         <v>37</v>
       </c>
-      <c r="E75" t="s">
+      <c r="F75" t="s">
         <v>127</v>
       </c>
-      <c r="F75">
-        <f>SUM(G75:U75)</f>
+      <c r="G75">
+        <f>SUM(H75:V75)</f>
         <v>1</v>
       </c>
-      <c r="K75">
+      <c r="L75">
         <f>1</f>
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A76">
         <v>57</v>
       </c>
@@ -2625,18 +3100,21 @@
       <c r="C76" t="s">
         <v>5</v>
       </c>
-      <c r="D76">
+      <c r="D76" t="s">
+        <v>209</v>
+      </c>
+      <c r="E76">
         <v>38</v>
       </c>
-      <c r="E76" t="s">
+      <c r="F76" t="s">
         <v>129</v>
       </c>
-      <c r="F76">
-        <f>SUM(G76:U76)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G76">
+        <f>SUM(H76:V76)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A77">
         <v>61</v>
       </c>
@@ -2646,18 +3124,21 @@
       <c r="C77" t="s">
         <v>5</v>
       </c>
-      <c r="D77">
+      <c r="D77" t="s">
+        <v>134</v>
+      </c>
+      <c r="E77">
         <v>38</v>
       </c>
-      <c r="E77" t="s">
+      <c r="F77" t="s">
         <v>129</v>
       </c>
-      <c r="F77">
-        <f>SUM(G77:U77)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G77">
+        <f>SUM(H77:V77)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A78">
         <v>8</v>
       </c>
@@ -2667,15 +3148,18 @@
       <c r="C78" t="s">
         <v>15</v>
       </c>
-      <c r="D78">
+      <c r="D78" t="s">
+        <v>210</v>
+      </c>
+      <c r="E78">
         <v>39</v>
       </c>
-      <c r="F78">
-        <f>SUM(G78:U78)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G78">
+        <f>SUM(H78:V78)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A79">
         <v>15</v>
       </c>
@@ -2685,60 +3169,72 @@
       <c r="C79" t="s">
         <v>15</v>
       </c>
-      <c r="D79">
+      <c r="D79" t="s">
+        <v>211</v>
+      </c>
+      <c r="E79">
         <v>39</v>
       </c>
-      <c r="F79">
-        <f>SUM(G79:U79)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G79">
+        <f>SUM(H79:V79)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A80">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="B80" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C80" t="s">
-        <v>5</v>
-      </c>
-      <c r="F80">
-        <f>SUM(G80:U80)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="D80" t="s">
+        <v>212</v>
+      </c>
+      <c r="G80">
+        <f>SUM(H80:V80)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A81">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B81" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C81" t="s">
         <v>10</v>
       </c>
-      <c r="F81">
-        <f>SUM(G81:U81)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D81" t="s">
+        <v>213</v>
+      </c>
+      <c r="G81">
+        <f>SUM(H81:V81)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A82">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="B82" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="C82" t="s">
-        <v>10</v>
-      </c>
-      <c r="F82">
-        <f>SUM(G82:U82)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="D82" t="s">
+        <v>214</v>
+      </c>
+      <c r="G82">
+        <f>SUM(H82:V82)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A83">
         <v>82</v>
       </c>
@@ -2748,24 +3244,27 @@
       <c r="C83" t="s">
         <v>32</v>
       </c>
-      <c r="F83">
-        <f>SUM(G83:U83)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="I84" t="s">
+      <c r="D83" t="s">
+        <v>215</v>
+      </c>
+      <c r="G83">
+        <f>SUM(H83:V83)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="J84" t="s">
         <v>132</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K84">
-      <sortCondition ref="D1"/>
+  <autoFilter ref="A1:L1" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L84">
+      <sortCondition ref="E1:E84"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E84">
-    <sortCondition ref="D1:D84"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F84">
+    <sortCondition ref="E1:E84"/>
   </sortState>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0249999999999999" bottom="1.0249999999999999" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
